--- a/RiskUnit/reports/risk_hesabati_rehberlik.xlsx
+++ b/RiskUnit/reports/risk_hesabati_rehberlik.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B-7854a9d6fc</t>
+          <t>B-949799ba38</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.44</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="7">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="8">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.114</v>
+        <v>0.141</v>
       </c>
     </row>
     <row r="10">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -656,19 +656,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İnflyasiyanın hədəf diapazonundan yuxarı olması: ehtimal 57%, skor 25 (P 5 × T 5, ölçü: inflyasiya)</t>
+          <t>İnflyasiyanın hədəf diapazonundan yuxarı olması: ehtimal 47%, skor 20 (P 4 × T 5, ölçü: inflyasiya)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>B-7854a9d6fc</t>
+          <t>B-949799ba38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -683,93 +683,85 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Büdcə balansının pisləşməsi: ehtimal 35%, skor 20 (P 4 × T 5, ölçü: büdcə)</t>
+          <t>Neft qiymətinin kəskin enməsi: ehtimal 48%, skor 16 (P 4 × T 4, ölçü: qeyri-neft ÜDM)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>B-7854a9d6fc</t>
+          <t>B-949799ba38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yüksək prioritet</t>
+          <t>göstərici həddi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>yüksək</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
+          <t>orta</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neft qiymətinin kəskin enməsi: ehtimal 26%, skor 15 (P 3 × T 5, ölçü: qeyri-neft ÜDM)</t>
+          <t>Regional geosiyasi risk (Rusiya, Ukrayna, İsrail, Türkiyə ortası): son dəyər 1.134 (2026-09), tarixi paylanmanın 91-cı faizi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>B-7854a9d6fc</t>
+          <t>B-949799ba38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yüksək prioritet</t>
+          <t>göstərici həddi</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>yüksək</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>R14</t>
-        </is>
-      </c>
+          <t>orta</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Enerji keçidi: karbohidrogen tələbinin struktur azalması: ehtimal 25%, skor 12 (P 3 × T 4, ölçü: qeyri-neft ÜDM)</t>
+          <t>FR10 izləmə siyahısındakı emal sahələri: 3 (2025)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>B-7854a9d6fc</t>
+          <t>B-949799ba38</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>göstərici həddi</t>
+          <t>baza köhnəlib</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -777,27 +769,31 @@
           <t>orta</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Regional geosiyasi risk (Rusiya, Ukrayna, İsrail, Türkiyə ortası): son dəyər 1.134 (2026-09), tarixi paylanmanın 91-cı faizi</t>
+          <t>2027: Brent mərkəzi yolu 84 USD (canlı) — makro fərziyyə 69 USD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>B-7854a9d6fc</t>
+          <t>B-949799ba38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>göstərici həddi</t>
+          <t>gündəlik monitor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -805,27 +801,31 @@
           <t>orta</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FR10 izləmə siyahısındakı emal sahələri: 3 (2025)</t>
+          <t>Brent (spot): 114 (2026-09-29), z = 2.7 — xəbərdarlıq ↑</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>B-7854a9d6fc</t>
+          <t>B-949799ba38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>baza köhnəlib</t>
+          <t>gündəlik monitor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -840,24 +840,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2027: canlı məlumatla şərtləndirilmiş qeyri-neft artımının medianı 7.4% — makro baza yolu 5.4%. Fərq ≥ 1 f.b.: makro modelin Brent fərziyyəsinin yenilənməsi tövsiyə olunur</t>
+          <t>Brent 2026 illik ortası (YTD + spot): 98.36 (2026-09-29), z = 6.9 — xəbərdarlıq ↑</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>B-7854a9d6fc</t>
+          <t>B-949799ba38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>baza köhnəlib</t>
+          <t>gündəlik monitor</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -872,12 +872,308 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2027: Brent mərkəzi yolu 84 USD (canlı) — makro fərziyyə 69 USD</t>
+          <t>Azeri Light (proksi) vs FR1 ixrac qiyməti: 114.6 (2026-09-29), z = 3.0 — xəbərdarlıq ↑</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>B-7854a9d6fc</t>
+          <t>B-949799ba38</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>gündəlik monitor</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>orta</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Dövlət büdcəsi xərcləri: icra (illik planın %-i): 54.83 (2026-08-01), z = -2.4 — xəbərdarlıq ↓</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>B-949799ba38</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>gündəlik monitor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>orta</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dövlət büdcəsinin balansı (Yanvar–ay) vs illik fərziyyə: 3716 (2026-08-01), z = 4.5 — xəbərdarlıq ↑</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>B-949799ba38</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>gündəlik monitor</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>orta</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ARDNF aktivləri vs Nazirlik ilsonu fərziyyəsi: 7.26e+04 (2026-06-30), z = 4.6 — xəbərdarlıq ↑</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>B-949799ba38</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>məlumat köhnəlib</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>orta</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>minfin (Maliyyə Nazirliyi: təsdiq olunmuş büdcə göstəriciləri): son müşahidə 2025-01-01, 643 gün — köhnə; status: keş: şəbəkə yoxdur</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>B-949799ba38</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>model riski</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>orta</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Proqnoz qeyri-müəyyənliyi / model riski: model riski (P×T deyil): köhnəlməmiş konsensus (fr1, imf, mspec) ilə baza fərqi; köhnəlmiş xaric: bu60;caem;v8; hədd 0.5 f.b.; əlverişsiz fərq 1.04 f.b. (hədd 0.5 f.b.; alternativ paylanma FR2_model_risk.csv)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>B-949799ba38</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>məlumat köhnəlib</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>aşağı</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>dsk_macro: son müşahidə 2026-08-01 (66 gün)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>B-949799ba38</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>məlumat köhnəlib</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>aşağı</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>dsk_cpi: son müşahidə 2026-08-01 (66 gün)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>B-949799ba38</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>məlumat köhnəlib</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>aşağı</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>dsk_tables: son müşahidə 2026-04-01 (188 gün)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>B-949799ba38</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>məlumat köhnəlib</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>aşağı</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>minfin: son müşahidə 2026-03-01 (219 gün)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>B-949799ba38</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>məlumat köhnəlib</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>aşağı</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sofaz: son müşahidə 2026-06-30 (98 gün)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>B-949799ba38</t>
         </is>
       </c>
     </row>
@@ -896,9 +1192,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
@@ -945,11 +1241,7 @@
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="4" t="inlineStr"/>
       <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
+      <c r="F2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -964,10 +1256,14 @@
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>R01</t>
+        </is>
+      </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
     </row>
@@ -979,29 +1275,17 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>R15</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>R08</t>
-        </is>
-      </c>
+          <t>R08;R09;R15</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr"/>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>R07</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>R14</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>R01</t>
-        </is>
-      </c>
+          <t>R07;R14</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1011,27 +1295,23 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>R09;R10</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R02;R18</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>R05;R04</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>R03</t>
-        </is>
-      </c>
+          <t>R05;R04;R11</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R13;R03</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1322,11 @@
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
       <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
@@ -1058,23 +1342,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="53" customWidth="1" min="3" max="3"/>
+    <col width="51" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="52" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1169,19 +1453,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.56965</v>
+        <v>0.4745</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3.669490402094498</v>
+        <v>3.668669484212645</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>5</v>
@@ -1192,7 +1476,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M2" s="4" t="inlineStr">
         <is>
@@ -1211,44 +1495,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Büdcə balansının pisləşməsi</t>
+          <t>Neft qiymətinin kəskin enməsi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>MAL</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.35045</v>
+        <v>0.4781</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.148235826232445</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-2.705239605565848</v>
       </c>
       <c r="H3" t="n">
-        <v>2.470352241074798</v>
+        <v>0.243348499141978</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>büdcə</t>
+          <t>qeyri-neft ÜDM</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
@@ -1257,7 +1541,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Maliyyə Nazirliyi</t>
+          <t>Maliyyə Nazirliyi; ARDNF</t>
         </is>
       </c>
     </row>
@@ -1267,33 +1551,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R01</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Neft qiymətinin kəskin enməsi</t>
+          <t>Qeyri-neft artımının kəskin zəifləməsi (Growth-at-Risk)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MAL</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.25915</v>
+        <v>0.141</v>
       </c>
       <c r="F4" t="n">
-        <v>3.794102890626076</v>
+        <v>1.851448413476265</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.067202462121368</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3074710592717911</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -1304,16 +1588,16 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
-      </c>
-      <c r="M4" s="4" t="inlineStr">
-        <is>
-          <t>yüksək</t>
+        <v>10</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>orta</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Maliyyə Nazirliyi; ARDNF</t>
+          <t>İqtisadiyyat Nazirliyi</t>
         </is>
       </c>
     </row>
@@ -1323,53 +1607,53 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Enerji keçidi: karbohidrogen tələbinin struktur azalması</t>
+          <t>Manatın məzənnəsinə təzyiq və devalvasiya</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>MAL</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.2464</v>
+        <v>0.09805</v>
       </c>
       <c r="F5" t="n">
-        <v>1.116033344672777</v>
+        <v>0.1865832516563455</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3366753595725854</v>
+        <v>4.098709226511697</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2971816583871961</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>qeyri-neft ÜDM</t>
+          <t>inflyasiya</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
-      </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>yüksək</t>
+        <v>10</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>orta</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>İqtisadiyyat Nazirliyi; ARDNF</t>
+          <t>Mərkəzi Bank (AMB)</t>
         </is>
       </c>
     </row>
@@ -1379,36 +1663,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R13</t>
+          <t>R07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Qeyri-neft artımının kəskin zəifləməsi (Growth-at-Risk)</t>
+          <t>Pul baratlarının kəskin azalması</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>XSI</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.11365</v>
+        <v>0.22365</v>
       </c>
       <c r="F6" t="n">
-        <v>2.364622600798294</v>
+        <v>0.6681913253608902</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1416,7 +1700,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1425,7 +1709,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>İqtisadiyyat Nazirliyi</t>
+          <t>İqtisadiyyat Nazirliyi; Mərkəzi Bank (AMB)</t>
         </is>
       </c>
     </row>
@@ -1435,30 +1719,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R07</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pul baratlarının kəskin azalması</t>
+          <t>Enerji keçidi: karbohidrogen tələbinin struktur azalması</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>XSI</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.22675</v>
+        <v>0.2497</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6656929709300472</v>
+        <v>0.5563236516274656</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-1.170294823351427</v>
       </c>
       <c r="H7" t="n">
-        <v>-0</v>
+        <v>0.1326579915023616</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -1481,7 +1765,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>İqtisadiyyat Nazirliyi; Mərkəzi Bank (AMB)</t>
+          <t>İqtisadiyyat Nazirliyi; ARDNF</t>
         </is>
       </c>
     </row>
@@ -1491,36 +1775,36 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R03</t>
+          <t>R05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Manatın məzənnəsinə təzyiq və devalvasiya</t>
+          <t>Tərəfdaş ölkələrdə iqtisadi tənəzzül</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MAL</t>
+          <t>XSI</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.06955</v>
+        <v>0.14235</v>
       </c>
       <c r="F8" t="n">
-        <v>1.47293381575668</v>
+        <v>0.6890986223274053</v>
       </c>
       <c r="G8" t="n">
-        <v>2.910512125228284</v>
+        <v>-0.2345258142648071</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>0.05433034510967913</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1528,7 +1812,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1537,7 +1821,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Mərkəzi Bank (AMB)</t>
+          <t>İqtisadiyyat Nazirliyi</t>
         </is>
       </c>
     </row>
@@ -1547,30 +1831,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R05</t>
+          <t>R04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tərəfdaş ölkələrdə iqtisadi tənəzzül</t>
+          <t>Bank sektorunda aktiv keyfiyyətinin pisləşməsi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>XSI</t>
+          <t>MAL</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.14235</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7027831408466546</v>
+        <v>0.3661327650727651</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2115962470150763</v>
+        <v>0.09038000000000002</v>
       </c>
       <c r="H9" t="n">
-        <v>0.006823598852171158</v>
+        <v>0.04519000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
@@ -1593,7 +1877,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>İqtisadiyyat Nazirliyi</t>
+          <t>Mərkəzi Bank (AMB)</t>
         </is>
       </c>
     </row>
@@ -1603,30 +1887,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R04</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bank sektorunda aktiv keyfiyyətinin pisləşməsi</t>
+          <t>Büdcə balansının pisləşməsi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MAL</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.10115</v>
+        <v>0.0873</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3600702224419179</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.08988500000000001</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0449425</v>
+        <v>0.6435914763817874</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -1636,7 +1920,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>qeyri-neft ÜDM</t>
+          <t>büdcə</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -1649,7 +1933,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Mərkəzi Bank (AMB)</t>
+          <t>Maliyyə Nazirliyi</t>
         </is>
       </c>
     </row>
@@ -1659,36 +1943,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R08</t>
+          <t>R16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Güclü zəlzələ</t>
+          <t>Rəqabət mühitinin pisləşməsi</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.19875</v>
+        <v>0.46545</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1331906582023991</v>
+        <v>0.09043112090604466</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.1385008395736144</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1893688159302816</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1696,16 +1980,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>orta</t>
+        <v>4</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>aşağı</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Fövqəladə Hallar Nazirliyi</t>
+          <t>Rəqabətin Mühafizəsi Agentliyi; İqtisadiyyat Nazirliyi</t>
         </is>
       </c>
     </row>
@@ -1715,36 +1999,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R16</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rəqabət mühitinin pisləşməsi</t>
+          <t>Maliyyə şəraitinin sərtləşməsi (kredit faizi)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>MAL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.4587</v>
+        <v>0.089</v>
       </c>
       <c r="F12" t="n">
-        <v>0.09117440608021352</v>
+        <v>0.1961004415830367</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1402497511200027</v>
+        <v>-0.06713093437657885</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0.03221603411784797</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1761,7 +2045,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Rəqabətin Mühafizəsi Agentliyi; İqtisadiyyat Nazirliyi</t>
+          <t>Mərkəzi Bank (AMB)</t>
         </is>
       </c>
     </row>
@@ -1771,36 +2055,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R02</t>
+          <t>R06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Maliyyə şəraitinin sərtləşməsi (kredit faizi)</t>
+          <t>Regional geosiyasi eskalasiya</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MAL</t>
+          <t>XSI</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.089</v>
+        <v>0.4090909090909091</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1998000082434331</v>
+        <v>-0.1195370181539843</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.06051050456662047</v>
+        <v>0.0347866658476323</v>
       </c>
       <c r="H13" t="n">
-        <v>0.003742686557178457</v>
+        <v>-0.00520413097235117</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1817,7 +2101,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Mərkəzi Bank (AMB)</t>
+          <t>Xarici İşlər Nazirliyi; İqtisadiyyat Nazirliyi</t>
         </is>
       </c>
     </row>
@@ -1827,12 +2111,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R06</t>
+          <t>R18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Regional geosiyasi eskalasiya</t>
+          <t>Dünya ərzaq qiymətlərinin şoku</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1841,26 +2125,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.078</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1338987494596827</v>
+        <v>-0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01441614211438756</v>
+        <v>0.7298276429986488</v>
       </c>
       <c r="H14" t="n">
-        <v>0.001753147065580487</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>qeyri-neft ÜDM</t>
+          <t>inflyasiya</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -1873,7 +2157,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Xarici İşlər Nazirliyi; İqtisadiyyat Nazirliyi</t>
+          <t>İqtisadiyyat Nazirliyi; Kənd Təsərrüfatı Nazirliyi; Mərkəzi Bank (AMB)</t>
         </is>
       </c>
     </row>
@@ -1883,30 +2167,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Emal sənayesi sahələrində maliyyə gərginliyi</t>
+          <t>Güclü zəlzələ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SEK</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.16055</v>
+        <v>0.196</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03243337121827462</v>
+        <v>0.08834150820121449</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.01274086849070601</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0.05368884380968081</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
@@ -1929,7 +2213,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>İqtisadiyyat Nazirliyi</t>
+          <t>Fövqəladə Hallar Nazirliyi</t>
         </is>
       </c>
     </row>
@@ -1953,10 +2237,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.1478</v>
+        <v>0.155</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09034017982592826</v>
+        <v>0.09101555699852792</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1965,7 +2249,7 @@
         <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -1976,7 +2260,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1995,33 +2279,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Daşqın və Xəzər dənizinin səviyyəsinin dəyişməsi</t>
+          <t>Emal sənayesi sahələrində maliyyə gərginliyi</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>SEK</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.09925</v>
+        <v>0.1652</v>
       </c>
       <c r="F17" t="n">
-        <v>0.08836498740554156</v>
+        <v>0.02818943688677864</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04503750000000001</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04503750000000001</v>
+        <v>-0</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -2032,16 +2316,184 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>aşağı</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>İqtisadiyyat Nazirliyi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Daşqın və Xəzər dənizinin səviyyəsinin dəyişməsi</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TEB</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.10565</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.08951291528632276</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.04471749999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.04471749999999999</v>
+      </c>
+      <c r="I18" t="n">
         <v>2</v>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>qeyri-neft ÜDM</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>aşağı</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Fövqəladə Hallar Nazirliyi; Ekologiya və Təbii Sərvətlər Nazirliyi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Qeyri-neft idxal qiymətlərinin kəskin artımı</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>XSI</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.04515</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5492635197976067</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>inflyasiya</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>aşağı</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>İqtisadiyyat Nazirliyi; Mərkəzi Bank (AMB)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Proqnoz qeyri-müəyyənliyi / model riski</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DAX</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.040805</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>qeyri-neft ÜDM</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>ayrıca göstərici</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>İqtisadiyyat Nazirliyi (proqnoz koordinasiyası); Maliyyə Nazirliyi</t>
         </is>
       </c>
     </row>
@@ -2056,16 +2508,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
+    <col width="51" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -2123,7 +2575,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -2136,7 +2588,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>T01;T02;T03;T09</t>
+          <t>T01;T02;T03;T09;T26;T28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2191,7 +2643,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -2204,7 +2656,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>T02;T05;T06</t>
+          <t>T02;T05;T06;T27</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2361,7 +2813,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -2374,7 +2826,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>T13;T14</t>
+          <t>T13;T14;T29</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2429,7 +2881,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -2442,7 +2894,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>T16;T17</t>
+          <t>T16;T17;T29</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2463,7 +2915,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -2476,7 +2928,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>T01;T02;T18</t>
+          <t>T01;T02;T18;T26;T27;T28;T29</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2497,7 +2949,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -2510,7 +2962,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>T06;T19</t>
+          <t>T06;T19;T24;T25</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2531,7 +2983,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
@@ -2544,7 +2996,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>T08;T09;T20</t>
+          <t>T08;T09;T20;T28</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2565,7 +3017,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -2578,7 +3030,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>T01;T03;T21</t>
+          <t>T01;T03;T21;T28</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2650,6 +3102,108 @@
         </is>
       </c>
       <c r="H17" t="inlineStr">
+        <is>
+          <t>ödənilib</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Qeyri-neft idxal qiymətlərinin kəskin artımı</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>T25</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ödənilib</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Dünya ərzaq qiymətlərinin şoku</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>T24</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ödənilib</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Proqnoz qeyri-müəyyənliyi / model riski</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>T30</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>ödənilib</t>
         </is>

--- a/RiskUnit/reports/risk_hesabati_rehberlik.xlsx
+++ b/RiskUnit/reports/risk_hesabati_rehberlik.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -505,7 +505,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="8">
@@ -576,7 +576,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -656,19 +656,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>İnflyasiyanın hədəf diapazonundan yuxarı olması: ehtimal 47%, skor 20 (P 4 × T 5, ölçü: inflyasiya)</t>
+          <t>İnflyasiyanın hədəf diapazonundan yuxarı olması: ehtimal 48%, skor 20 (P 4 × T 5, ölçü: inflyasiya)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -693,14 +693,14 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,14 +721,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -749,14 +749,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -781,14 +781,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -813,14 +813,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -845,14 +845,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -877,14 +877,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -909,14 +909,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -941,14 +941,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -973,14 +973,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -996,19 +996,19 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>minfin (Maliyyə Nazirliyi: təsdiq olunmuş büdcə göstəriciləri): son müşahidə 2025-01-01, 643 gün — köhnə; status: keş: şəbəkə yoxdur</t>
+          <t>minfin (Maliyyə Nazirliyi: təsdiq olunmuş büdcə göstəriciləri): son müşahidə 2025-01-01, 644 gün — köhnə; status: keş: şəbəkə yoxdur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1028,19 +1028,19 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Proqnoz qeyri-müəyyənliyi / model riski: model riski (P×T deyil): köhnəlməmiş konsensus (fr1, imf, mspec) ilə baza fərqi; köhnəlmiş xaric: bu60;caem;v8; hədd 0.5 f.b.; əlverişsiz fərq 1.04 f.b. (hədd 0.5 f.b.; alternativ paylanma FR2_model_risk.csv)</t>
+          <t>Proqnoz qeyri-müəyyənliyi / model riski: model riski (P×T deyil): köhnəlməmiş konsensus (fr1, imf, mspec) ilə baza fərqi; köhnəlmiş xaric: bu60;caem;v8; hədd 0.5 f.b.; əlverişsiz fərq 1.23 f.b. (hədd 0.5 f.b.; alternativ paylanma FR2_model_risk.csv)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1056,19 +1056,19 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>dsk_macro: son müşahidə 2026-08-01 (66 gün)</t>
+          <t>brent: son müşahidə 2026-09-29 (8 gün)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1084,19 +1084,19 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>dsk_cpi: son müşahidə 2026-08-01 (66 gün)</t>
+          <t>dsk_macro: son müşahidə 2026-08-01 (67 gün)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1112,19 +1112,19 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>dsk_tables: son müşahidə 2026-04-01 (188 gün)</t>
+          <t>dsk_cpi: son müşahidə 2026-08-01 (67 gün)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1140,19 +1140,19 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>minfin: son müşahidə 2026-03-01 (219 gün)</t>
+          <t>dsk_tables: son müşahidə 2026-04-01 (189 gün)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1168,12 +1168,40 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>sofaz: son müşahidə 2026-06-30 (98 gün)</t>
+          <t>minfin: son müşahidə 2026-03-01 (220 gün)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B-949799ba38</t>
+          <t>B-d7e77e886f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>məlumat köhnəlib</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>aşağı</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sofaz: son müşahidə 2026-06-30 (99 gün)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>B-d7e77e886f</t>
         </is>
       </c>
     </row>
@@ -1453,13 +1481,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.4745</v>
+        <v>0.47525</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3.668669484212645</v>
+        <v>3.670617789226606</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1512,13 +1540,13 @@
         <v>0.4781</v>
       </c>
       <c r="F3" t="n">
-        <v>1.148235826232445</v>
+        <v>1.138379582543735</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.705239605565848</v>
+        <v>-2.69478577773629</v>
       </c>
       <c r="H3" t="n">
-        <v>0.243348499141978</v>
+        <v>0.2425556024249982</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
@@ -1565,10 +1593,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.141</v>
+        <v>0.1406</v>
       </c>
       <c r="F4" t="n">
-        <v>1.851448413476265</v>
+        <v>1.851298402304873</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1624,13 +1652,13 @@
         <v>0.09805</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1865832516563455</v>
+        <v>0.1970342089263448</v>
       </c>
       <c r="G5" t="n">
         <v>4.098709226511697</v>
       </c>
       <c r="H5" t="n">
-        <v>-0</v>
+        <v>0.03566587654352295</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -1736,13 +1764,13 @@
         <v>0.2497</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5563236516274656</v>
+        <v>0.5511284474619335</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.170294823351427</v>
+        <v>-1.164559939744585</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1326579915023616</v>
+        <v>0.1269041995082851</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -1792,13 +1820,13 @@
         <v>0.14235</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6890986223274053</v>
+        <v>0.6829990166512481</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2345258142648071</v>
+        <v>-0.2276000371656484</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05433034510967913</v>
+        <v>0.05345996454349649</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -1901,7 +1929,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.0873</v>
+        <v>0.0963</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -1910,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6435914763817874</v>
+        <v>0.6387268468251253</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
@@ -2016,13 +2044,13 @@
         <v>0.089</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1961004415830367</v>
+        <v>0.1943394187931896</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.06713093437657885</v>
+        <v>-0.06512676188932408</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03221603411784797</v>
+        <v>0.03198832797338956</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
@@ -2072,13 +2100,13 @@
         <v>0.4090909090909091</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1195370181539843</v>
+        <v>-0.1192364995457633</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0347866658476323</v>
+        <v>0.0344480214961637</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.00520413097235117</v>
+        <v>-0.00510986474365599</v>
       </c>
       <c r="I13" t="n">
         <v>4</v>
@@ -2184,13 +2212,13 @@
         <v>0.196</v>
       </c>
       <c r="F15" t="n">
-        <v>0.08834150820121449</v>
+        <v>0.08868952185854784</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01274086849070601</v>
+        <v>0.01234050647732735</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05368884380968081</v>
+        <v>0.05372688901177071</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
@@ -2464,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1.040805</v>
+        <v>1.227415</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
